--- a/Documents/Salary Matrix and Companies.xlsx
+++ b/Documents/Salary Matrix and Companies.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unitedlaboratoriesinc-my.sharepoint.com/personal/gsvictoria_unilab_com_ph/Documents/Documents/JO TOOL/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitLab\joboffer\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="8_{37C3383D-FEE1-4758-8FD9-2042457BD7A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{271D5F08-D645-4D72-ADCA-ED01B2303B2A}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA3AA315-F765-453B-984C-A4CACD0DA30E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{575A86D5-35A8-4F74-AC7D-0A711BBBFAE5}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{575A86D5-35A8-4F74-AC7D-0A711BBBFAE5}"/>
   </bookViews>
   <sheets>
     <sheet name="UL AND ULSSI SALARY MATRIX" sheetId="1" r:id="rId1"/>
     <sheet name="COMPANIES IN SCOPE" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="35">
   <si>
     <r>
       <t>SG</t>
@@ -248,6 +249,24 @@
   </si>
   <si>
     <t>Note: These are sample values to be updated by the business admin on production.</t>
+  </si>
+  <si>
+    <t>10​</t>
+  </si>
+  <si>
+    <t>9​</t>
+  </si>
+  <si>
+    <t>8​</t>
+  </si>
+  <si>
+    <t>7​</t>
+  </si>
+  <si>
+    <t>6​</t>
+  </si>
+  <si>
+    <t>5​</t>
   </si>
 </sst>
 </file>
@@ -427,7 +446,7 @@
     <xf numFmtId="43" fontId="4" fillId="4" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1007,65 +1026,398 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11B58D6F-5A18-4302-8E20-0B6B6CE05E6F}">
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="39.26953125" customWidth="1"/>
+    <col min="4" max="4" width="90.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B2">
+        <v>3100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B3">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B4">
+        <v>3300</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B5">
+        <v>3400</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B6">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B7">
+        <v>3600</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B8">
+        <v>3700</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B9">
+        <v>3800</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
+      <c r="B10">
+        <v>3900</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
         <v>19</v>
+      </c>
+      <c r="B11">
+        <v>4000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4835F8EF-6569-48A0-A7E4-1789142C8D83}">
+  <dimension ref="A2:H13"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="4" max="4" width="5.90625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="90.26953125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2">
+        <v>53000</v>
+      </c>
+      <c r="D2">
+        <v>69000</v>
+      </c>
+      <c r="E2">
+        <v>88500</v>
+      </c>
+      <c r="F2">
+        <v>103500</v>
+      </c>
+      <c r="H2" t="str">
+        <f>"update SalaryBands set Minimum="&amp;C2&amp;",Midpoint="&amp;D2&amp;",Maximum="&amp;E2&amp;",CompaRatio="&amp;F2&amp;" where Id="&amp;A2&amp;";"</f>
+        <v>update SalaryBands set Minimum=53000,Midpoint=69000,Maximum=88500,CompaRatio=103500 where Id=1;</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3">
+        <v>48000</v>
+      </c>
+      <c r="D3">
+        <v>62000</v>
+      </c>
+      <c r="E3">
+        <v>79500</v>
+      </c>
+      <c r="F3">
+        <v>93000</v>
+      </c>
+      <c r="H3" t="str">
+        <f t="shared" ref="H3:H13" si="0">"update SalaryBands set Minimum="&amp;C3&amp;",Midpoint="&amp;D3&amp;",Maximum="&amp;E3&amp;",CompaRatio="&amp;F3&amp;" where Id="&amp;A3&amp;";"</f>
+        <v>update SalaryBands set Minimum=48000,Midpoint=62000,Maximum=79500,CompaRatio=93000 where Id=2;</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4">
+        <v>44000</v>
+      </c>
+      <c r="D4">
+        <v>56000</v>
+      </c>
+      <c r="E4">
+        <v>72000</v>
+      </c>
+      <c r="F4">
+        <v>84000</v>
+      </c>
+      <c r="H4" t="str">
+        <f t="shared" si="0"/>
+        <v>update SalaryBands set Minimum=44000,Midpoint=56000,Maximum=72000,CompaRatio=84000 where Id=3;</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5">
+        <v>40000</v>
+      </c>
+      <c r="D5">
+        <v>50500</v>
+      </c>
+      <c r="E5">
+        <v>65500</v>
+      </c>
+      <c r="F5">
+        <v>75750</v>
+      </c>
+      <c r="H5" t="str">
+        <f t="shared" si="0"/>
+        <v>update SalaryBands set Minimum=40000,Midpoint=50500,Maximum=65500,CompaRatio=75750 where Id=4;</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6">
+        <v>36000</v>
+      </c>
+      <c r="D6">
+        <v>45000</v>
+      </c>
+      <c r="E6">
+        <v>58500</v>
+      </c>
+      <c r="F6">
+        <v>67500</v>
+      </c>
+      <c r="H6" t="str">
+        <f t="shared" si="0"/>
+        <v>update SalaryBands set Minimum=36000,Midpoint=45000,Maximum=58500,CompaRatio=67500 where Id=5;</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7">
+        <v>33000</v>
+      </c>
+      <c r="D7">
+        <v>41500</v>
+      </c>
+      <c r="E7">
+        <v>54000</v>
+      </c>
+      <c r="F7">
+        <v>62250</v>
+      </c>
+      <c r="H7" t="str">
+        <f t="shared" si="0"/>
+        <v>update SalaryBands set Minimum=33000,Midpoint=41500,Maximum=54000,CompaRatio=62250 where Id=6;</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8">
+        <v>30000</v>
+      </c>
+      <c r="D8">
+        <v>38900</v>
+      </c>
+      <c r="E8">
+        <v>49800</v>
+      </c>
+      <c r="F8">
+        <v>58350</v>
+      </c>
+      <c r="H8" t="str">
+        <f t="shared" si="0"/>
+        <v>update SalaryBands set Minimum=30000,Midpoint=38900,Maximum=49800,CompaRatio=58350 where Id=7;</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9">
+        <v>26000</v>
+      </c>
+      <c r="D9">
+        <v>34100</v>
+      </c>
+      <c r="E9">
+        <v>43400</v>
+      </c>
+      <c r="F9">
+        <v>51150</v>
+      </c>
+      <c r="H9" t="str">
+        <f t="shared" si="0"/>
+        <v>update SalaryBands set Minimum=26000,Midpoint=34100,Maximum=43400,CompaRatio=51150 where Id=8;</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10">
+        <v>23000</v>
+      </c>
+      <c r="D10">
+        <v>29800</v>
+      </c>
+      <c r="E10">
+        <v>38600</v>
+      </c>
+      <c r="F10">
+        <v>44700</v>
+      </c>
+      <c r="H10" t="str">
+        <f t="shared" si="0"/>
+        <v>update SalaryBands set Minimum=23000,Midpoint=29800,Maximum=38600,CompaRatio=44700 where Id=9;</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11">
+        <v>20000</v>
+      </c>
+      <c r="D11">
+        <v>26000</v>
+      </c>
+      <c r="E11">
+        <v>33800</v>
+      </c>
+      <c r="F11">
+        <v>39000</v>
+      </c>
+      <c r="H11" t="str">
+        <f t="shared" si="0"/>
+        <v>update SalaryBands set Minimum=20000,Midpoint=26000,Maximum=33800,CompaRatio=39000 where Id=10;</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12">
+        <v>18000</v>
+      </c>
+      <c r="D12">
+        <v>22700</v>
+      </c>
+      <c r="E12">
+        <v>30600</v>
+      </c>
+      <c r="F12">
+        <v>34050</v>
+      </c>
+      <c r="H12" t="str">
+        <f t="shared" si="0"/>
+        <v>update SalaryBands set Minimum=18000,Midpoint=22700,Maximum=30600,CompaRatio=34050 where Id=11;</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13">
+        <v>14500</v>
+      </c>
+      <c r="D13">
+        <v>19750</v>
+      </c>
+      <c r="E13">
+        <v>25000</v>
+      </c>
+      <c r="F13">
+        <v>29625</v>
+      </c>
+      <c r="H13" t="str">
+        <f t="shared" si="0"/>
+        <v>update SalaryBands set Minimum=14500,Midpoint=19750,Maximum=25000,CompaRatio=29625 where Id=12;</v>
       </c>
     </row>
   </sheetData>
@@ -1074,6 +1426,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E905CC0FB92AAA4DB52D2F535F34E1A4" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7bad061a8825ea9617a7c961fc07043e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2b589191-c6d3-45d0-95e2-4cff73607ad1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1909b04aa68677c3b4b49f76a278a155" ns2:_="">
     <xsd:import namespace="2b589191-c6d3-45d0-95e2-4cff73607ad1"/>
@@ -1211,15 +1572,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -1227,13 +1579,36 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B808305-B15A-4033-955A-92042A7717EC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{87ADA86B-99F9-4C5D-A5AD-94C19549C78C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{87ADA86B-99F9-4C5D-A5AD-94C19549C78C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B808305-B15A-4033-955A-92042A7717EC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="2b589191-c6d3-45d0-95e2-4cff73607ad1"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3ED1ADD9-6F65-4680-A0F3-F889454ED79D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3ED1ADD9-6F65-4680-A0F3-F889454ED79D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>